--- a/Data/EC/NIT-9008813213.xlsx
+++ b/Data/EC/NIT-9008813213.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F160722D-8888-47FC-A0FC-6E587DB21550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE029E0-CBD1-4363-99E9-0688F0DC910B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B77E8D6A-EE12-439C-99D7-40C187D24441}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E4A0B0BF-29F1-46BF-90EE-23301B100911}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="76">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -107,6 +107,9 @@
     <t>REGINA MAR A SANTANA ESCORCIA</t>
   </si>
   <si>
+    <t>2607</t>
+  </si>
+  <si>
     <t>2606</t>
   </si>
   <si>
@@ -219,6 +222,18 @@
   </si>
   <si>
     <t>2212</t>
+  </si>
+  <si>
+    <t>1111754270</t>
+  </si>
+  <si>
+    <t>LYDER ALFREDO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>1002302593</t>
+  </si>
+  <si>
+    <t>IVAN ALBERTO OCHOA VILLAREAL</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -617,22 +632,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F156C07D-41CC-9626-5196-A6948355741E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C332E5B1-0908-A645-4CF8-8D9D783658A8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -641,7 +656,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -654,7 +669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -983,27 +998,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925D98F1-E90C-425F-8CF2-94BDD581EE14}">
-  <dimension ref="B2:J68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7A9B-5E66-4AF7-9ED5-5818FDA66F9A}">
+  <dimension ref="B2:J71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.06640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1012,7 +1027,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1023,7 +1038,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1034,7 +1049,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1045,10 +1060,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1061,8 +1076,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1077,15 +1092,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2928050</v>
+        <v>3133732</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1093,27 +1108,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F13" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1133,16 +1148,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1165,7 +1180,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1188,7 +1203,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1211,7 +1226,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1234,7 +1249,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1257,7 +1272,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1280,7 +1295,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1318,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1326,7 +1341,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1349,7 +1364,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1387,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1410,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1433,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1441,7 +1456,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1464,7 +1479,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1502,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1510,7 +1525,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1533,7 +1548,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1571,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1594,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1617,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1625,7 +1640,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1648,7 +1663,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1671,7 +1686,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1709,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1717,7 +1732,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1755,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1778,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1801,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1824,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1832,7 +1847,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1870,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1866,7 +1881,7 @@
         <v>21</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F47" s="18">
         <v>70000</v>
@@ -1878,7 +1893,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1904,7 @@
         <v>21</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F48" s="18">
         <v>70000</v>
@@ -1901,7 +1916,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1924,7 +1939,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1947,7 +1962,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1985,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +2008,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2016,7 +2031,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2039,38 +2054,38 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D55" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>43</v>
-      </c>
       <c r="F55" s="18">
-        <v>52490</v>
+        <v>70000</v>
       </c>
       <c r="G55" s="18">
-        <v>1437451</v>
+        <v>1750000</v>
       </c>
       <c r="H55" s="19"/>
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>44</v>
@@ -2085,21 +2100,21 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F57" s="18">
-        <v>55691</v>
+        <v>52490</v>
       </c>
       <c r="G57" s="18">
         <v>1437451</v>
@@ -2108,15 +2123,15 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E58" s="16" t="s">
         <v>47</v>
@@ -2131,15 +2146,15 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E59" s="16" t="s">
         <v>48</v>
@@ -2154,44 +2169,44 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D60" s="17" t="s">
-        <v>56</v>
-      </c>
       <c r="E60" s="16" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F60" s="18">
-        <v>90000</v>
+        <v>55691</v>
       </c>
       <c r="G60" s="18">
-        <v>2500000</v>
+        <v>1437451</v>
       </c>
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>58</v>
       </c>
       <c r="F61" s="18">
-        <v>100000</v>
+        <v>90000</v>
       </c>
       <c r="G61" s="18">
         <v>2500000</v>
@@ -2200,57 +2215,126 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B62" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D62" s="23" t="s">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="D62" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E62" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F62" s="24">
+      <c r="F62" s="18">
+        <v>100000</v>
+      </c>
+      <c r="G62" s="18">
+        <v>2500000</v>
+      </c>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F63" s="18">
         <v>20000</v>
       </c>
-      <c r="G62" s="24">
+      <c r="G63" s="18">
         <v>2500000</v>
       </c>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25"/>
-      <c r="J62" s="26"/>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B67" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" s="32"/>
-      <c r="H67" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B68" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="32"/>
-      <c r="H68" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="18">
+        <v>65645</v>
+      </c>
+      <c r="G64" s="18">
+        <v>1641120</v>
+      </c>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="24">
+        <v>70037</v>
+      </c>
+      <c r="G65" s="24">
+        <v>1750905</v>
+      </c>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="26"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" s="32"/>
+      <c r="H70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="32"/>
+      <c r="H71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H70:J70"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
